--- a/PLAN Y PROGRAMA DE CAP MODIFICADO ID 2026.xlsx
+++ b/PLAN Y PROGRAMA DE CAP MODIFICADO ID 2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpineda.JPINEDA\OneDrive\Desktop\sistema_capacitacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LICONSA\OneDrive\Desktop\LUZ ESTRELLA-ESTADIA-MAYO-AGOSTO2026\SILVESTRE CARGA DE INFORMACION\PLANTILLAS 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -8453,10 +8453,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -8469,10 +8465,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -8483,6 +8475,14 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -13645,73 +13645,73 @@
       <c r="S12" s="7"/>
     </row>
     <row r="13" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="221" t="s">
+      <c r="A13" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="221"/>
-      <c r="C13" s="221"/>
-      <c r="D13" s="221"/>
-      <c r="E13" s="221"/>
-      <c r="F13" s="221"/>
-      <c r="G13" s="221"/>
-      <c r="H13" s="221"/>
-      <c r="I13" s="221"/>
-      <c r="J13" s="221"/>
-      <c r="K13" s="221"/>
-      <c r="L13" s="221"/>
-      <c r="M13" s="221"/>
-      <c r="N13" s="221"/>
-      <c r="O13" s="221"/>
-      <c r="P13" s="221"/>
-      <c r="Q13" s="221"/>
-      <c r="R13" s="221"/>
-      <c r="S13" s="221"/>
+      <c r="B13" s="228"/>
+      <c r="C13" s="228"/>
+      <c r="D13" s="228"/>
+      <c r="E13" s="228"/>
+      <c r="F13" s="228"/>
+      <c r="G13" s="228"/>
+      <c r="H13" s="228"/>
+      <c r="I13" s="228"/>
+      <c r="J13" s="228"/>
+      <c r="K13" s="228"/>
+      <c r="L13" s="228"/>
+      <c r="M13" s="228"/>
+      <c r="N13" s="228"/>
+      <c r="O13" s="228"/>
+      <c r="P13" s="228"/>
+      <c r="Q13" s="228"/>
+      <c r="R13" s="228"/>
+      <c r="S13" s="228"/>
     </row>
     <row r="14" spans="1:20" ht="40.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="221" t="s">
+      <c r="A14" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="221"/>
-      <c r="C14" s="221"/>
-      <c r="D14" s="221"/>
-      <c r="E14" s="221"/>
-      <c r="F14" s="221"/>
-      <c r="G14" s="221"/>
-      <c r="H14" s="221"/>
-      <c r="I14" s="221"/>
-      <c r="J14" s="221"/>
-      <c r="K14" s="221"/>
-      <c r="L14" s="221"/>
-      <c r="M14" s="221"/>
-      <c r="N14" s="221"/>
-      <c r="O14" s="221"/>
-      <c r="P14" s="221"/>
-      <c r="Q14" s="221"/>
-      <c r="R14" s="221"/>
-      <c r="S14" s="221"/>
+      <c r="B14" s="228"/>
+      <c r="C14" s="228"/>
+      <c r="D14" s="228"/>
+      <c r="E14" s="228"/>
+      <c r="F14" s="228"/>
+      <c r="G14" s="228"/>
+      <c r="H14" s="228"/>
+      <c r="I14" s="228"/>
+      <c r="J14" s="228"/>
+      <c r="K14" s="228"/>
+      <c r="L14" s="228"/>
+      <c r="M14" s="228"/>
+      <c r="N14" s="228"/>
+      <c r="O14" s="228"/>
+      <c r="P14" s="228"/>
+      <c r="Q14" s="228"/>
+      <c r="R14" s="228"/>
+      <c r="S14" s="228"/>
     </row>
     <row r="15" spans="1:20" ht="39.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="221" t="s">
+      <c r="A15" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="221"/>
-      <c r="C15" s="221"/>
-      <c r="D15" s="221"/>
-      <c r="E15" s="221"/>
-      <c r="F15" s="221"/>
-      <c r="G15" s="221"/>
-      <c r="H15" s="221"/>
-      <c r="I15" s="221"/>
-      <c r="J15" s="221"/>
-      <c r="K15" s="221"/>
-      <c r="L15" s="221"/>
-      <c r="M15" s="221"/>
-      <c r="N15" s="221"/>
-      <c r="O15" s="221"/>
-      <c r="P15" s="221"/>
-      <c r="Q15" s="221"/>
-      <c r="R15" s="221"/>
-      <c r="S15" s="221"/>
+      <c r="B15" s="228"/>
+      <c r="C15" s="228"/>
+      <c r="D15" s="228"/>
+      <c r="E15" s="228"/>
+      <c r="F15" s="228"/>
+      <c r="G15" s="228"/>
+      <c r="H15" s="228"/>
+      <c r="I15" s="228"/>
+      <c r="J15" s="228"/>
+      <c r="K15" s="228"/>
+      <c r="L15" s="228"/>
+      <c r="M15" s="228"/>
+      <c r="N15" s="228"/>
+      <c r="O15" s="228"/>
+      <c r="P15" s="228"/>
+      <c r="Q15" s="228"/>
+      <c r="R15" s="228"/>
+      <c r="S15" s="228"/>
       <c r="T15" s="10"/>
     </row>
     <row r="16" spans="1:20" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -14024,7 +14024,7 @@
       <c r="T22" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U22" s="222">
+      <c r="U22" s="221">
         <f>SUM(R22:R25)</f>
         <v>8</v>
       </c>
@@ -14073,7 +14073,7 @@
       <c r="T23" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U23" s="223"/>
+      <c r="U23" s="222"/>
     </row>
     <row r="24" spans="1:21" s="40" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="30" t="str">
@@ -14119,7 +14119,7 @@
       <c r="T24" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U24" s="223"/>
+      <c r="U24" s="222"/>
     </row>
     <row r="25" spans="1:21" s="40" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="30" t="str">
@@ -14165,7 +14165,7 @@
       <c r="T25" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U25" s="224"/>
+      <c r="U25" s="223"/>
     </row>
     <row r="26" spans="1:21" s="59" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="30" t="str">
@@ -14292,7 +14292,7 @@
       <c r="T28" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U28" s="222">
+      <c r="U28" s="221">
         <f>SUM(' PLAN Y PROGRAMA ANUAL 2026'!$R28:$R30)</f>
         <v>6</v>
       </c>
@@ -14341,7 +14341,7 @@
       <c r="T29" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U29" s="223"/>
+      <c r="U29" s="222"/>
     </row>
     <row r="30" spans="1:21" s="40" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="30" t="str">
@@ -14387,7 +14387,7 @@
       <c r="T30" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U30" s="224"/>
+      <c r="U30" s="223"/>
     </row>
     <row r="31" spans="1:21" s="40" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="30">
@@ -14914,7 +14914,7 @@
       <c r="T40" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U40" s="222">
+      <c r="U40" s="221">
         <f>SUM(R40:R41)</f>
         <v>4</v>
       </c>
@@ -14960,7 +14960,7 @@
       <c r="T41" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U41" s="224"/>
+      <c r="U41" s="223"/>
     </row>
     <row r="42" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="30">
@@ -15018,7 +15018,7 @@
       <c r="T42" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U42" s="222">
+      <c r="U42" s="221">
         <f>SUM(' PLAN Y PROGRAMA ANUAL 2026'!$R42:$R43)</f>
         <v>4</v>
       </c>
@@ -15067,7 +15067,7 @@
       <c r="T43" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U43" s="224"/>
+      <c r="U43" s="223"/>
     </row>
     <row r="44" spans="1:21" s="40" customFormat="1" ht="68.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="30">
@@ -15570,7 +15570,7 @@
       <c r="T53" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U53" s="222">
+      <c r="U53" s="221">
         <f>SUM(R53:R54)</f>
         <v>2</v>
       </c>
@@ -15619,7 +15619,7 @@
       <c r="T54" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U54" s="224"/>
+      <c r="U54" s="223"/>
     </row>
     <row r="55" spans="1:21" s="40" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="30">
@@ -15792,7 +15792,7 @@
       <c r="T58" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U58" s="222">
+      <c r="U58" s="221">
         <f>SUM(R58:R60)</f>
         <v>6</v>
       </c>
@@ -15841,7 +15841,7 @@
       <c r="T59" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U59" s="223"/>
+      <c r="U59" s="222"/>
     </row>
     <row r="60" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="30" t="str">
@@ -15887,7 +15887,7 @@
       <c r="T60" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U60" s="224"/>
+      <c r="U60" s="223"/>
     </row>
     <row r="61" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="30">
@@ -16277,7 +16277,7 @@
       <c r="T69" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U69" s="222">
+      <c r="U69" s="221">
         <f>SUM(R69:R70)</f>
         <v>42</v>
       </c>
@@ -16323,7 +16323,7 @@
       <c r="T70" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U70" s="224"/>
+      <c r="U70" s="223"/>
     </row>
     <row r="71" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="30">
@@ -17140,7 +17140,7 @@
       <c r="T89" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U89" s="222">
+      <c r="U89" s="221">
         <f>SUM(R89:R91)</f>
         <v>6</v>
       </c>
@@ -17189,7 +17189,7 @@
       <c r="T90" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U90" s="223"/>
+      <c r="U90" s="222"/>
     </row>
     <row r="91" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="30" t="str">
@@ -17235,7 +17235,7 @@
       <c r="T91" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U91" s="224"/>
+      <c r="U91" s="223"/>
     </row>
     <row r="92" spans="1:21" s="40" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="30">
@@ -17964,7 +17964,7 @@
         <f>IFERROR(VLOOKUP(O107, '[1]CURSOS 2025'!A:B, 2, FALSE), "")</f>
         <v>S/COSTO</v>
       </c>
-      <c r="U107" s="222">
+      <c r="U107" s="221">
         <f>SUM(R107:R108)</f>
         <v>40</v>
       </c>
@@ -18010,7 +18010,7 @@
       <c r="T108" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U108" s="224"/>
+      <c r="U108" s="223"/>
     </row>
     <row r="109" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="30">
@@ -18448,7 +18448,7 @@
         <f>IFERROR(VLOOKUP(O117, '[1]CURSOS 2025'!A:B, 2, FALSE), "")</f>
         <v>S/COSTO</v>
       </c>
-      <c r="U117" s="222">
+      <c r="U117" s="221">
         <f>SUM(R117:R118)</f>
         <v>40</v>
       </c>
@@ -18494,7 +18494,7 @@
       <c r="T118" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U118" s="224"/>
+      <c r="U118" s="223"/>
     </row>
     <row r="119" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="30">
@@ -21250,7 +21250,7 @@
       <c r="T174" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U174" s="222">
+      <c r="U174" s="221">
         <f>SUM(R174:R175)</f>
         <v>44</v>
       </c>
@@ -21296,7 +21296,7 @@
       <c r="T175" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U175" s="224"/>
+      <c r="U175" s="223"/>
     </row>
     <row r="176" spans="1:21" s="40" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="30">
@@ -22671,7 +22671,7 @@
       <c r="T203" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U203" s="222">
+      <c r="U203" s="221">
         <f>SUM(R203:R204)</f>
         <v>45</v>
       </c>
@@ -22717,7 +22717,7 @@
       <c r="T204" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U204" s="224"/>
+      <c r="U204" s="223"/>
     </row>
     <row r="205" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="30">
@@ -24220,7 +24220,7 @@
       <c r="T234" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U234" s="222">
+      <c r="U234" s="221">
         <f>SUM(R234:R235)</f>
         <v>40</v>
       </c>
@@ -24266,7 +24266,7 @@
       <c r="T235" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U235" s="224"/>
+      <c r="U235" s="223"/>
     </row>
     <row r="236" spans="1:21" s="40" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="30">
@@ -29027,7 +29027,7 @@
       <c r="T338" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U338" s="222">
+      <c r="U338" s="221">
         <f>SUM(R338:R341)</f>
         <v>8</v>
       </c>
@@ -29076,7 +29076,7 @@
       <c r="T339" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U339" s="223"/>
+      <c r="U339" s="222"/>
     </row>
     <row r="340" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A340" s="30" t="str">
@@ -29122,7 +29122,7 @@
       <c r="T340" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U340" s="223"/>
+      <c r="U340" s="222"/>
     </row>
     <row r="341" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A341" s="30" t="str">
@@ -29168,7 +29168,7 @@
       <c r="T341" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U341" s="224"/>
+      <c r="U341" s="223"/>
     </row>
     <row r="342" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A342" s="30">
@@ -29360,7 +29360,7 @@
       <c r="T345" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U345" s="222">
+      <c r="U345" s="221">
         <f>SUM(R345:R346)</f>
         <v>4</v>
       </c>
@@ -29409,7 +29409,7 @@
       <c r="T346" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U346" s="224"/>
+      <c r="U346" s="223"/>
     </row>
     <row r="347" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A347" s="30">
@@ -29559,7 +29559,7 @@
       <c r="T349" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U349" s="222">
+      <c r="U349" s="221">
         <f>SUM(R349:R352)</f>
         <v>8</v>
       </c>
@@ -29605,7 +29605,7 @@
       <c r="T350" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U350" s="223"/>
+      <c r="U350" s="222"/>
     </row>
     <row r="351" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A351" s="30" t="str">
@@ -29651,7 +29651,7 @@
       <c r="T351" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U351" s="223"/>
+      <c r="U351" s="222"/>
     </row>
     <row r="352" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A352" s="30" t="str">
@@ -29697,7 +29697,7 @@
       <c r="T352" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U352" s="224"/>
+      <c r="U352" s="223"/>
     </row>
     <row r="353" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A353" s="30">
@@ -29939,7 +29939,7 @@
       <c r="T357" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U357" s="222">
+      <c r="U357" s="221">
         <f>SUM(R357:R359)</f>
         <v>6</v>
       </c>
@@ -29988,7 +29988,7 @@
       <c r="T358" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U358" s="223"/>
+      <c r="U358" s="222"/>
     </row>
     <row r="359" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A359" s="30" t="str">
@@ -30034,7 +30034,7 @@
       <c r="T359" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U359" s="224"/>
+      <c r="U359" s="223"/>
     </row>
     <row r="360" spans="1:21" s="40" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A360" s="30">
@@ -30230,7 +30230,7 @@
       <c r="T363" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U363" s="226">
+      <c r="U363" s="224">
         <f>SUM(R363:R365)</f>
         <v>6</v>
       </c>
@@ -30279,7 +30279,7 @@
       <c r="T364" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U364" s="227"/>
+      <c r="U364" s="225"/>
     </row>
     <row r="365" spans="1:21" s="40" customFormat="1" ht="68.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A365" s="30" t="str">
@@ -30325,7 +30325,7 @@
       <c r="T365" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U365" s="228"/>
+      <c r="U365" s="226"/>
     </row>
     <row r="366" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A366" s="30">
@@ -38679,7 +38679,7 @@
       <c r="T546" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U546" s="226">
+      <c r="U546" s="224">
         <f>SUM(R546:R548)</f>
         <v>6</v>
       </c>
@@ -38728,7 +38728,7 @@
       <c r="T547" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U547" s="227"/>
+      <c r="U547" s="225"/>
     </row>
     <row r="548" spans="1:21" s="40" customFormat="1" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A548" s="30" t="str">
@@ -38774,7 +38774,7 @@
       <c r="T548" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U548" s="228"/>
+      <c r="U548" s="226"/>
     </row>
     <row r="549" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A549" s="30">
@@ -38893,7 +38893,7 @@
       <c r="T550" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U550" s="226">
+      <c r="U550" s="224">
         <f>SUM(R550:R552)</f>
         <v>6</v>
       </c>
@@ -38942,7 +38942,7 @@
       <c r="T551" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U551" s="227"/>
+      <c r="U551" s="225"/>
     </row>
     <row r="552" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A552" s="30" t="str">
@@ -38988,7 +38988,7 @@
       <c r="T552" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U552" s="227"/>
+      <c r="U552" s="225"/>
     </row>
     <row r="553" spans="1:21" s="40" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A553" s="30">
@@ -43036,7 +43036,7 @@
       <c r="T638" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U638" s="222">
+      <c r="U638" s="221">
         <f>SUM(R638:R639)</f>
         <v>60</v>
       </c>
@@ -43082,7 +43082,7 @@
       <c r="T639" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U639" s="224"/>
+      <c r="U639" s="223"/>
     </row>
     <row r="640" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A640" s="30">
@@ -43140,7 +43140,7 @@
       <c r="T640" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U640" s="222">
+      <c r="U640" s="221">
         <f>SUM(R640:R642)</f>
         <v>42</v>
       </c>
@@ -43189,7 +43189,7 @@
       <c r="T641" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U641" s="223"/>
+      <c r="U641" s="222"/>
     </row>
     <row r="642" spans="1:22" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A642" s="30"/>
@@ -43232,7 +43232,7 @@
       <c r="T642" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U642" s="224"/>
+      <c r="U642" s="223"/>
     </row>
     <row r="643" spans="1:22" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A643" s="30">
@@ -43400,7 +43400,7 @@
       <c r="T645" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U645" s="222">
+      <c r="U645" s="221">
         <f>SUM(R645:R647)</f>
         <v>72</v>
       </c>
@@ -43446,7 +43446,7 @@
       <c r="T646" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U646" s="223"/>
+      <c r="U646" s="222"/>
     </row>
     <row r="647" spans="1:22" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A647" s="30"/>
@@ -43489,7 +43489,7 @@
       <c r="T647" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U647" s="224"/>
+      <c r="U647" s="223"/>
     </row>
     <row r="648" spans="1:22" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A648" s="30">
@@ -43761,7 +43761,7 @@
       <c r="T652" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U652" s="222">
+      <c r="U652" s="221">
         <f>SUM(R652:R654)</f>
         <v>6</v>
       </c>
@@ -43810,7 +43810,7 @@
       <c r="T653" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U653" s="223"/>
+      <c r="U653" s="222"/>
     </row>
     <row r="654" spans="1:22" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A654" s="30" t="str">
@@ -43856,7 +43856,7 @@
       <c r="T654" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U654" s="224"/>
+      <c r="U654" s="223"/>
     </row>
     <row r="655" spans="1:22" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A655" s="30">
@@ -43958,7 +43958,7 @@
       <c r="T656" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U656" s="222">
+      <c r="U656" s="221">
         <f>SUM(R656:R659)</f>
         <v>4</v>
       </c>
@@ -44007,7 +44007,7 @@
       <c r="T657" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U657" s="223"/>
+      <c r="U657" s="222"/>
     </row>
     <row r="658" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A658" s="30" t="str">
@@ -44053,7 +44053,7 @@
       <c r="T658" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U658" s="223"/>
+      <c r="U658" s="222"/>
     </row>
     <row r="659" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A659" s="30"/>
@@ -44096,7 +44096,7 @@
       <c r="T659" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U659" s="224"/>
+      <c r="U659" s="223"/>
     </row>
     <row r="660" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A660" s="30">
@@ -44244,7 +44244,7 @@
       <c r="T662" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U662" s="222">
+      <c r="U662" s="221">
         <f>SUM(R662:R663)</f>
         <v>12</v>
       </c>
@@ -44290,7 +44290,7 @@
       <c r="T663" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U663" s="224"/>
+      <c r="U663" s="223"/>
     </row>
     <row r="664" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A664" s="30">
@@ -44849,7 +44849,7 @@
       <c r="T674" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U674" s="222">
+      <c r="U674" s="221">
         <f>SUM(R674:R677)</f>
         <v>8</v>
       </c>
@@ -44898,7 +44898,7 @@
       <c r="T675" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U675" s="223"/>
+      <c r="U675" s="222"/>
     </row>
     <row r="676" spans="1:21" s="40" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A676" s="30" t="str">
@@ -44944,7 +44944,7 @@
       <c r="T676" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U676" s="223"/>
+      <c r="U676" s="222"/>
     </row>
     <row r="677" spans="1:21" s="40" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A677" s="30" t="str">
@@ -44990,7 +44990,7 @@
       <c r="T677" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U677" s="224"/>
+      <c r="U677" s="223"/>
     </row>
     <row r="678" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A678" s="30">
@@ -45640,7 +45640,7 @@
       <c r="T691" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U691" s="222">
+      <c r="U691" s="221">
         <f>SUM(R691:R692)</f>
         <v>4</v>
       </c>
@@ -45689,7 +45689,7 @@
       <c r="T692" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U692" s="224"/>
+      <c r="U692" s="223"/>
     </row>
     <row r="693" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A693" s="30">
@@ -46198,7 +46198,7 @@
       <c r="T703" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U703" s="222">
+      <c r="U703" s="221">
         <f>SUM(R703:R705)</f>
         <v>6</v>
       </c>
@@ -46247,7 +46247,7 @@
       <c r="T704" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U704" s="223"/>
+      <c r="U704" s="222"/>
     </row>
     <row r="705" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A705" s="30" t="str">
@@ -46293,7 +46293,7 @@
       <c r="T705" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U705" s="224"/>
+      <c r="U705" s="223"/>
     </row>
     <row r="706" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A706" s="30">
@@ -46489,7 +46489,7 @@
       <c r="T709" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U709" s="222">
+      <c r="U709" s="221">
         <f>SUM(R709:R711)</f>
         <v>6</v>
       </c>
@@ -46538,7 +46538,7 @@
       <c r="T710" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U710" s="223"/>
+      <c r="U710" s="222"/>
     </row>
     <row r="711" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A711" s="30" t="str">
@@ -46584,7 +46584,7 @@
       <c r="T711" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U711" s="224"/>
+      <c r="U711" s="223"/>
     </row>
     <row r="712" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A712" s="30">
@@ -48359,7 +48359,7 @@
       <c r="T746" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U746" s="222">
+      <c r="U746" s="221">
         <f>SUM(R746:R749)</f>
         <v>4</v>
       </c>
@@ -48408,7 +48408,7 @@
       <c r="T747" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U747" s="223"/>
+      <c r="U747" s="222"/>
     </row>
     <row r="748" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A748" s="30" t="str">
@@ -48454,7 +48454,7 @@
       <c r="T748" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U748" s="223"/>
+      <c r="U748" s="222"/>
     </row>
     <row r="749" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A749" s="30"/>
@@ -48497,7 +48497,7 @@
       <c r="T749" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U749" s="224"/>
+      <c r="U749" s="223"/>
     </row>
     <row r="750" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A750" s="30">
@@ -49899,7 +49899,7 @@
       <c r="T779" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U779" s="222">
+      <c r="U779" s="221">
         <f>SUM(R779:R781)</f>
         <v>6</v>
       </c>
@@ -49948,7 +49948,7 @@
       <c r="T780" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U780" s="223"/>
+      <c r="U780" s="222"/>
     </row>
     <row r="781" spans="1:21" s="40" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A781" s="30"/>
@@ -49991,7 +49991,7 @@
       <c r="T781" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="U781" s="224"/>
+      <c r="U781" s="223"/>
     </row>
     <row r="782" spans="1:21" s="40" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A782" s="30">
@@ -50428,10 +50428,10 @@
       <c r="E793" s="99" t="s">
         <v>1702</v>
       </c>
-      <c r="O793" s="225" t="s">
+      <c r="O793" s="227" t="s">
         <v>1703</v>
       </c>
-      <c r="P793" s="225"/>
+      <c r="P793" s="227"/>
       <c r="Q793" s="93"/>
       <c r="R793" s="2"/>
       <c r="S793" s="100"/>
@@ -50545,10 +50545,10 @@
       <c r="E808" s="99" t="s">
         <v>1704</v>
       </c>
-      <c r="O808" s="225" t="s">
+      <c r="O808" s="227" t="s">
         <v>1705</v>
       </c>
-      <c r="P808" s="225"/>
+      <c r="P808" s="227"/>
       <c r="Q808" s="1"/>
       <c r="R808" s="2"/>
       <c r="T808" s="102"/>
@@ -50558,16 +50558,16 @@
       <c r="E809" s="99" t="s">
         <v>1706</v>
       </c>
-      <c r="L809" s="225" t="s">
+      <c r="L809" s="227" t="s">
         <v>1707</v>
       </c>
-      <c r="M809" s="225"/>
-      <c r="N809" s="225"/>
-      <c r="O809" s="225"/>
-      <c r="P809" s="225"/>
-      <c r="Q809" s="225"/>
-      <c r="R809" s="225"/>
-      <c r="S809" s="225"/>
+      <c r="M809" s="227"/>
+      <c r="N809" s="227"/>
+      <c r="O809" s="227"/>
+      <c r="P809" s="227"/>
+      <c r="Q809" s="227"/>
+      <c r="R809" s="227"/>
+      <c r="S809" s="227"/>
       <c r="T809" s="102"/>
       <c r="U809" s="104"/>
     </row>
@@ -50578,28 +50578,6 @@
   </sheetData>
   <autoFilter ref="A17:XFC787"/>
   <mergeCells count="38">
-    <mergeCell ref="U662:U663"/>
-    <mergeCell ref="U345:U346"/>
-    <mergeCell ref="U674:U677"/>
-    <mergeCell ref="U174:U175"/>
-    <mergeCell ref="U638:U639"/>
-    <mergeCell ref="U640:U642"/>
-    <mergeCell ref="U645:U647"/>
-    <mergeCell ref="U656:U659"/>
-    <mergeCell ref="U652:U654"/>
-    <mergeCell ref="U349:U352"/>
-    <mergeCell ref="U550:U552"/>
-    <mergeCell ref="U546:U548"/>
-    <mergeCell ref="U363:U365"/>
-    <mergeCell ref="U357:U359"/>
-    <mergeCell ref="L809:S809"/>
-    <mergeCell ref="U709:U711"/>
-    <mergeCell ref="U703:U705"/>
-    <mergeCell ref="U691:U692"/>
-    <mergeCell ref="O793:P793"/>
-    <mergeCell ref="O808:P808"/>
-    <mergeCell ref="U779:U781"/>
-    <mergeCell ref="U746:U749"/>
     <mergeCell ref="A13:S13"/>
     <mergeCell ref="A14:S14"/>
     <mergeCell ref="A15:S15"/>
@@ -50613,9 +50591,31 @@
     <mergeCell ref="U107:U108"/>
     <mergeCell ref="U117:U118"/>
     <mergeCell ref="U234:U235"/>
+    <mergeCell ref="L809:S809"/>
+    <mergeCell ref="U709:U711"/>
+    <mergeCell ref="U703:U705"/>
+    <mergeCell ref="U691:U692"/>
+    <mergeCell ref="O793:P793"/>
+    <mergeCell ref="O808:P808"/>
+    <mergeCell ref="U779:U781"/>
     <mergeCell ref="U58:U60"/>
     <mergeCell ref="U89:U91"/>
+    <mergeCell ref="U652:U654"/>
+    <mergeCell ref="U349:U352"/>
+    <mergeCell ref="U550:U552"/>
+    <mergeCell ref="U546:U548"/>
+    <mergeCell ref="U363:U365"/>
+    <mergeCell ref="U357:U359"/>
     <mergeCell ref="U203:U204"/>
+    <mergeCell ref="U174:U175"/>
+    <mergeCell ref="U638:U639"/>
+    <mergeCell ref="U640:U642"/>
+    <mergeCell ref="U645:U647"/>
+    <mergeCell ref="U656:U659"/>
+    <mergeCell ref="U746:U749"/>
+    <mergeCell ref="U662:U663"/>
+    <mergeCell ref="U345:U346"/>
+    <mergeCell ref="U674:U677"/>
   </mergeCells>
   <conditionalFormatting sqref="T788">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="C/COSTO">
